--- a/Packages/PackImport/Sources/PackImport/Resources/Samples/sample-phrases.xlsx
+++ b/Packages/PackImport/Sources/PackImport/Resources/Samples/sample-phrases.xlsx
@@ -178,8 +178,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -208,11 +215,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -224,7 +237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -232,7 +245,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -240,186 +253,186 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Packages/PackImport/Sources/PackImport/Resources/Samples/sample-phrases.xlsx
+++ b/Packages/PackImport/Sources/PackImport/Resources/Samples/sample-phrases.xlsx
@@ -193,15 +193,21 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -209,13 +215,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -225,7 +246,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -261,178 +291,178 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="4" t="s">
         <v>51</v>
       </c>
     </row>
